--- a/tests/mung/fixtures/sumprod_z1_2026-07-06.xlsx
+++ b/tests/mung/fixtures/sumprod_z1_2026-07-06.xlsx
@@ -12,14 +12,13 @@
     <sheet name="incomplete" sheetId="3" r:id="rId3"/>
     <sheet name="incomplete_uniq" sheetId="4" r:id="rId4"/>
     <sheet name="calc" sheetId="5" r:id="rId5"/>
-    <sheet name="calc_aug" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="29">
   <si>
     <t>entity</t>
   </si>
@@ -230,21 +229,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Frame4" displayName="Frame4" ref="A1:E36" totalsRowShown="0">
-  <autoFilter ref="A1:E36"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="entity" dataDxfId="0"/>
-    <tableColumn id="2" name="concept" dataDxfId="0"/>
-    <tableColumn id="3" name="pertype" dataDxfId="0"/>
-    <tableColumn id="4" name="period" dataDxfId="0"/>
-    <tableColumn id="5" name="rolly_amt" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Frame5" displayName="Frame5" ref="A1:F36" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Frame4" displayName="Frame4" ref="A1:F36" totalsRowShown="0">
   <autoFilter ref="A1:F36"/>
   <tableColumns count="6">
     <tableColumn id="1" name="entity" dataDxfId="0"/>
@@ -1761,7 +1746,7 @@
         <v>0.25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
@@ -1781,7 +1766,7 @@
         <v>0.25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
@@ -1821,7 +1806,7 @@
         <v>-1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>8</v>
@@ -1841,7 +1826,7 @@
         <v>-1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
@@ -1999,7 +1984,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
@@ -2008,12 +1993,12 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
@@ -2022,7 +2007,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2036,12 +2021,12 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2050,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2064,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2083,7 +2068,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -2106,7 +2091,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2120,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2134,7 +2119,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2148,7 +2133,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2162,12 +2147,12 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -2176,7 +2161,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2190,7 +2175,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2204,12 +2189,12 @@
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -2218,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2231,631 +2216,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="3">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="3">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="3">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="3">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="3">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="3">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="3">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="3">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="3">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="3">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="3">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="3">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="3">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="3">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="3">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="3">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="3">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="3">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="3">
-        <v>119</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/tests/mung/fixtures/sumprod_z1_2026-07-06.xlsx
+++ b/tests/mung/fixtures/sumprod_z1_2026-07-06.xlsx
@@ -1626,7 +1626,7 @@
         <v>0.75</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
@@ -1646,7 +1646,7 @@
         <v>0.75</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -1706,7 +1706,7 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -1726,7 +1726,7 @@
         <v>0.5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
@@ -1806,7 +1806,7 @@
         <v>-1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>8</v>
@@ -1826,7 +1826,7 @@
         <v>-1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
@@ -1926,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
@@ -1946,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
@@ -1993,12 +1993,12 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
@@ -2021,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2035,12 +2035,12 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
@@ -2049,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2063,12 +2063,12 @@
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -2077,7 +2077,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2091,7 +2091,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2105,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2119,7 +2119,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2133,12 +2133,12 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
@@ -2147,12 +2147,12 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -2161,7 +2161,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2175,12 +2175,12 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -2203,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
